--- a/Hand_edited_log/3/StudentsSolution.xlsx
+++ b/Hand_edited_log/3/StudentsSolution.xlsx
@@ -40,145 +40,181 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>anhnvhe163786</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
     <x:t>anhptphe170125</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
     <x:t>anhvqhe187074</x:t>
   </x:si>
   <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
     <x:t>daipvhe161222</x:t>
   </x:si>
   <x:si>
-    <x:t>4</x:t>
+    <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>datnthe187166</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
+    <x:t>6</x:t>
   </x:si>
   <x:si>
     <x:t>dongnkhe172307</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>dongtdhe171684</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
+    <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>ducnmhe182217</x:t>
   </x:si>
   <x:si>
-    <x:t>8</x:t>
+    <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>dungpvhe180060</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duongcqhe176062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>duynnhe176832</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>hailvhe186288</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>hieutmhe180724</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangnlhe180286</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HoangNLHE186662</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>hungnvhe161335</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>17</x:t>
   </x:si>
   <x:si>
     <x:t>huynlhe172025</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>kiemnvhe186025</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>LinhPNHE180370</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>sannxthe153321</x:t>
   </x:si>
   <x:si>
-    <x:t>17</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>Sondphe182318</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>tamtqhe181412</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tanhmhe181126</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
   </x:si>
   <x:si>
     <x:t>tientvhe186986</x:t>
   </x:si>
   <x:si>
-    <x:t>20</x:t>
+    <x:t>25</x:t>
   </x:si>
   <x:si>
     <x:t>trinvmhe181736</x:t>
   </x:si>
   <x:si>
-    <x:t>21</x:t>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>truonghnhe180891</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
+    <x:t>27</x:t>
   </x:si>
   <x:si>
     <x:t>TuanTVHE181340</x:t>
   </x:si>
   <x:si>
-    <x:t>23</x:t>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tungnlhe186756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29</x:t>
   </x:si>
   <x:si>
     <x:t>tungtthe173042</x:t>
@@ -552,7 +588,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G24"/>
+  <x:dimension ref="A1:G30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
@@ -1116,6 +1152,144 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
+      <x:c r="A28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
